--- a/data/trans_orig/P44D-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P44D-Edad-trans_orig.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2012 (tasa de respuesta: 98,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -712,7 +712,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6211</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2264</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10908</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -835,107 +835,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11908</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26228</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,07%</t>
         </is>
       </c>
     </row>
@@ -948,114 +948,114 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34681</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34681</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34681</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3486</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17832</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -1178,107 +1178,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27863</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23010</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28760</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58865</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49275</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -1291,114 +1291,114 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39341</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39341</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39341</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33823</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33823</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33823</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73164</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73164</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73164</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3016</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2937</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -1521,107 +1521,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22220</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24447</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60168</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -1634,114 +1634,114 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66121</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66121</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66121</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1938</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6208</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3541</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1095</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8116</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>16,63%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>38,11%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6211</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2906</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10283</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>43,83%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>72,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6687</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,93%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>32,61%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14969</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>25,5%</t>
         </is>
       </c>
     </row>
@@ -1864,107 +1864,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>24520</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>20250</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>26458</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>17754</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>20200</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>38</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>26228</t>
+          <t>42274</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>35575</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30458</t>
+          <t>45723</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -1977,22 +1977,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>26458</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>26458</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>26458</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2047,22 +2047,22 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>47753</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>47753</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>47753</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,7 +2084,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11885</t>
+          <t>25874</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>30070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14299</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7622</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>47920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -2207,107 +2207,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>98055</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27456</t>
+          <t>86832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39341</t>
+          <t>104747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23010</t>
+          <t>89479</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>78943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28193</t>
+          <t>97078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>170</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>58865</t>
+          <t>187534</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48957</t>
+          <t>173799</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65542</t>
+          <t>198286</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -2320,22 +2320,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39341</t>
+          <t>112706</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39341</t>
+          <t>112706</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39341</t>
+          <t>112706</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2355,22 +2355,22 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33823</t>
+          <t>109013</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33823</t>
+          <t>109013</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33823</t>
+          <t>109013</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2390,22 +2390,22 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>196</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>73164</t>
+          <t>221719</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>73164</t>
+          <t>221719</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73164</t>
+          <t>221719</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,1054 +2425,22 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario privado</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>3016</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9317</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>28,46%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2937</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8289</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>24,83%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>5953</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>1931</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>13637</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>20,62%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario público</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>29719</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>23418</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>32735</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>71,54%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>30449</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>25097</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>33386</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>75,17%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>60168</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>52484</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>64190</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>91,0%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>79,38%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>32735</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>32735</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>32735</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>33386</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>33386</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>33386</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>66121</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>66121</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>66121</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario privado</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1938</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6797</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>25,69%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3541</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1084</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>8172</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>38,38%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>5479</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>11510</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>24,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario público</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>24520</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>19661</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>26458</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>92,67%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>74,31%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>17754</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>13123</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>20211</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>83,37%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>61,62%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>94,91%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>42274</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>36243</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>45649</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>88,53%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>75,9%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>95,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>26458</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>26458</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>26458</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>21295</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>21295</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>21295</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>47753</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>47753</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>47753</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario privado</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>14651</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>7508</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>25516</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>22,64%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>19534</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>12550</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>30531</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>17,92%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>28,01%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>34185</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>23465</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>46731</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>15,42%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>21,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario público</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>98055</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>87190</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>105198</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>87,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>77,36%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>93,34%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>89479</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>78482</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>96463</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>82,08%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>71,99%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>88,49%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>187534</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>174988</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>198254</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>84,58%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>78,92%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>89,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>112706</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>112706</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>112706</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>109013</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>109013</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>109013</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>221719</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>221719</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>221719</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3485,7 +2453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3516,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2016 (tasa de respuesta: 93,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,7 +2659,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3701,107 +2669,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -3814,107 +2782,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22570</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7777</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10059</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30347</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24306</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -3927,114 +2895,114 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4044,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14263</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8161</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21854</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>43,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -4157,107 +3125,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28412</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67299</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59383</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -4270,114 +3238,114 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50266</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50266</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50266</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33513</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33513</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33513</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83779</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83779</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83779</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -4387,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6994</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -4500,107 +3468,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40181</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27329</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64326</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58131</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -4613,114 +3581,114 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42142</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42142</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28414</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28414</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28414</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70556</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70556</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70556</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -4730,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13422</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -4843,107 +3811,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22570</t>
+          <t>35893</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>31595</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25711</t>
+          <t>37633</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>33181</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>27475</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>35840</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>66</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>30347</t>
+          <t>69073</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24397</t>
+          <t>63245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34653</t>
+          <t>72356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -4956,22 +3924,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4991,22 +3959,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>35840</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>35840</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>35840</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5026,22 +3994,22 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>71</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>37819</t>
+          <t>74208</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37819</t>
+          <t>74208</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>37819</t>
+          <t>74208</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5063,7 +4031,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -5073,107 +4041,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14263</t>
+          <t>22912</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21496</t>
+          <t>32903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>21299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>35316</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>24879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>47632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -5186,107 +4154,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>129</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>134646</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28770</t>
+          <t>124655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41818</t>
+          <t>143002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31297</t>
+          <t>96400</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26486</t>
+          <t>87505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33513</t>
+          <t>102344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>211</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>67299</t>
+          <t>231046</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57943</t>
+          <t>218730</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73669</t>
+          <t>241483</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -5299,22 +4267,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>151</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50266</t>
+          <t>157558</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50266</t>
+          <t>157558</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50266</t>
+          <t>157558</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5334,22 +4302,22 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33513</t>
+          <t>108804</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33513</t>
+          <t>108804</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33513</t>
+          <t>108804</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5369,22 +4337,22 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>244</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>83779</t>
+          <t>266362</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>83779</t>
+          <t>266362</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83779</t>
+          <t>266362</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5404,1054 +4372,22 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario privado</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7054</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4269</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>9456</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>33,28%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>6230</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>2797</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>12097</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>17,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario público</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>40181</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>35088</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>42142</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>83,26%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>24145</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>18958</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>27343</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>84,98%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>66,72%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>96,23%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>64326</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>58459</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>67759</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>91,17%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>82,85%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>96,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>42142</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>42142</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>42142</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>28414</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>28414</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>28414</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>70556</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>70556</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>70556</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario privado</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2475</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>733</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6964</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2659</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>8097</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>22,59%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>5135</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1697</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>11020</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>14,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario público</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>35893</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>31404</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>37635</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>93,55%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>33181</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>27743</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>35840</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>92,58%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>77,41%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>69073</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>63188</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>72511</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>93,08%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>85,15%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>38368</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>38368</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>38368</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>35840</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>35840</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>35840</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>74208</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>74208</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>74208</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario privado</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>22912</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>14778</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>33053</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>20,98%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>12404</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>6591</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>19,33%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>35316</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>48185</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>13,26%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario público</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>134646</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>124505</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>142780</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>85,46%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>79,02%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>90,62%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>96400</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>87776</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>102213</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>88,6%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>80,67%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>231046</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>218177</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>241362</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>86,74%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>81,91%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>90,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>157558</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>157558</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>157558</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>108804</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>108804</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>108804</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>266362</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>266362</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>266362</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6464,7 +4400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6495,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde le realizaron dicha prueba de Cáncer de colon en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última prueba de cribado del cáncer de colon en 2023 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6670,7 +4606,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -6680,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6437</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -6793,107 +4729,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326735</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>303312</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333172</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>109</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65461</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>61036</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>195</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>392196</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>367916</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>402928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -6906,114 +4842,114 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333172</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72037</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72037</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72037</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405209</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405209</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405209</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7023,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16403</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34515</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36736</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46799</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -7136,107 +5072,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>188</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159000</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>259</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143461</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>137363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147644</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>447</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>302461</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>292398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>310864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -7249,114 +5185,114 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>183248</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>183248</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>183248</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>281</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155949</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155949</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>498</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339197</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339197</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339197</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7366,107 +5302,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27999</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -7479,107 +5415,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>226</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147756</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153526</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>266</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131252</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135502</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>492</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>279009</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>270238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285660</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -7592,114 +5528,114 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>249</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>163949</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>163949</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>163949</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143059</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143059</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143059</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>538</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307008</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307008</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7709,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30040</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>2237</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11038</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38895</t>
+          <t>14580</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -7822,107 +5758,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>147</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>326735</t>
+          <t>93738</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303132</t>
+          <t>88919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>332597</t>
+          <t>96467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>201</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>65461</t>
+          <t>103969</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60999</t>
+          <t>100302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68679</t>
+          <t>106142</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>348</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>392196</t>
+          <t>197707</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366314</t>
+          <t>192593</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>403514</t>
+          <t>201344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -7935,22 +5871,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>155</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>98794</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>98794</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>98794</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7970,22 +5906,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>210</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72037</t>
+          <t>108379</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72037</t>
+          <t>108379</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72037</t>
+          <t>108379</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8005,22 +5941,22 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>365</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>405209</t>
+          <t>207173</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>405209</t>
+          <t>207173</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>405209</t>
+          <t>207173</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8042,7 +5978,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -8052,107 +5988,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24248</t>
+          <t>51933</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33875</t>
+          <t>82658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>35281</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>131</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>36736</t>
+          <t>87214</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27251</t>
+          <t>45666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47522</t>
+          <t>113496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -8165,107 +6101,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>647</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>159000</t>
+          <t>727230</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>149373</t>
+          <t>696505</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167077</t>
+          <t>757430</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>835</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>143461</t>
+          <t>444142</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137994</t>
+          <t>435406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148210</t>
+          <t>451964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>302461</t>
+          <t>1171373</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>291675</t>
+          <t>1145091</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>311946</t>
+          <t>1212921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -8278,22 +6214,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>713</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>779163</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>779163</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>779163</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8313,22 +6249,22 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>900</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>155949</t>
+          <t>479423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>155949</t>
+          <t>479423</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>155949</t>
+          <t>479423</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8348,22 +6284,22 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1613</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>1258587</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>1258587</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>1258587</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8383,1054 +6319,22 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario privado</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>16193</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>10680</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>23516</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>14,34%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>11807</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>7799</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>17221</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>12,04%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>27999</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>20590</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>37475</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>12,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario público</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>147756</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>140433</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>153269</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>85,66%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>131252</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>125838</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>135260</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>87,96%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>279009</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>269533</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>286418</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>90,88%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>87,79%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>93,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>163949</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>163949</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>163949</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>143059</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>143059</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>143059</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>307008</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>307008</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>307008</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario privado</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5056</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2134</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>9413</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>4410</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7905</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>9466</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>5964</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>15015</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario público</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>93738</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>89381</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>96660</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>90,47%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>103969</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>100474</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>106247</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>95,93%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>197707</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>192158</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>201209</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>95,43%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>92,75%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>98794</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>98794</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>98794</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>108379</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>108379</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>108379</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>207173</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>207173</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>207173</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario privado</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>51933</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>21634</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>83117</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>35281</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>27874</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>43889</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>87214</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>46542</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>113303</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Servicio sanitario público</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>727230</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>696046</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>757529</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>89,33%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>444142</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>435534</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>451549</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>92,64%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>90,85%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>94,19%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1482</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1171373</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1145284</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1212045</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>91,0%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>96,3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>779163</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>779163</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>779163</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>479423</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>479423</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>479423</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>1613</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>1258587</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>1258587</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>1258587</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_orig/P44D-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P44D-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,19%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11908</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>19704</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30544</t>
+          <t>30674</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23889</t>
+          <t>25516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27863</t>
+          <t>27868</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>28227</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49275</t>
+          <t>47648</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66022</t>
+          <t>65290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10515</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>9149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22220</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24447</t>
+          <t>24237</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50704</t>
+          <t>51139</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64241</t>
+          <t>64923</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20250</t>
+          <t>20434</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>20209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>36747</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45723</t>
+          <t>45755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7959</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25874</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30070</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47920</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86832</t>
+          <t>87612</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104747</t>
+          <t>105288</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78943</t>
+          <t>79294</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97078</t>
+          <t>97486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173799</t>
+          <t>173042</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198286</t>
+          <t>198781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>13074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17906</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>25697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24306</t>
+          <t>24745</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34562</t>
+          <t>34612</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24396</t>
+          <t>24894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28412</t>
+          <t>28874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42105</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26411</t>
+          <t>26741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59383</t>
+          <t>58885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73263</t>
+          <t>74065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12425</t>
+          <t>12797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35148</t>
+          <t>35565</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>18901</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27329</t>
+          <t>27337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58131</t>
+          <t>57759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68451</t>
+          <t>67726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>32258</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37633</t>
+          <t>37588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27475</t>
+          <t>27732</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63245</t>
+          <t>62873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72356</t>
+          <t>72481</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>14371</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>32738</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21299</t>
+          <t>21487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>24014</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47632</t>
+          <t>47511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124655</t>
+          <t>124820</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143002</t>
+          <t>143187</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87505</t>
+          <t>87317</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102344</t>
+          <t>102259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>218730</t>
+          <t>218851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241483</t>
+          <t>242348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29860</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37293</t>
+          <t>22607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>326735</t>
+          <t>88119</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303312</t>
+          <t>80600</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>92595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65461</t>
+          <t>69993</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61036</t>
+          <t>64992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68701</t>
+          <t>73460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>392196</t>
+          <t>158111</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>367916</t>
+          <t>149648</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>402928</t>
+          <t>163418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>94995</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>94995</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>94995</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>72037</t>
+          <t>77260</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>72037</t>
+          <t>77260</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72037</t>
+          <t>77260</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>405209</t>
+          <t>172255</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>405209</t>
+          <t>172255</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>405209</t>
+          <t>172255</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24248</t>
+          <t>27089</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16403</t>
+          <t>18905</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34515</t>
+          <t>36952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>36736</t>
+          <t>41055</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28333</t>
+          <t>31186</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46799</t>
+          <t>51788</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>159000</t>
+          <t>166481</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148733</t>
+          <t>156618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>166845</t>
+          <t>174665</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>143461</t>
+          <t>161172</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137363</t>
+          <t>154244</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147644</t>
+          <t>165697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>302461</t>
+          <t>327653</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>292398</t>
+          <t>316920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>310864</t>
+          <t>337522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>193570</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>193570</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>193570</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>155949</t>
+          <t>175138</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>155949</t>
+          <t>175138</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>155949</t>
+          <t>175138</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>368708</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>368708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>368708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23456</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17174</t>
+          <t>18494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>29578</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>22231</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36770</t>
+          <t>39218</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>147756</t>
+          <t>160822</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140493</t>
+          <t>153502</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153526</t>
+          <t>166346</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>131252</t>
+          <t>144900</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125885</t>
+          <t>139061</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135502</t>
+          <t>148967</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>279009</t>
+          <t>305722</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>270238</t>
+          <t>296082</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>285660</t>
+          <t>313069</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>163949</t>
+          <t>177745</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>163949</t>
+          <t>177745</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163949</t>
+          <t>177745</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>143059</t>
+          <t>157555</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143059</t>
+          <t>157555</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143059</t>
+          <t>157555</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>307008</t>
+          <t>335300</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>307008</t>
+          <t>335300</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>307008</t>
+          <t>335300</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>11265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>93738</t>
+          <t>102205</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88919</t>
+          <t>96425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96467</t>
+          <t>105123</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>103969</t>
+          <t>115432</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100302</t>
+          <t>111690</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>106142</t>
+          <t>117943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>197707</t>
+          <t>217636</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192593</t>
+          <t>211151</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>201344</t>
+          <t>221504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>98794</t>
+          <t>107690</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>98794</t>
+          <t>107690</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>98794</t>
+          <t>107690</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>108379</t>
+          <t>120049</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>108379</t>
+          <t>120049</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>108379</t>
+          <t>120049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>207173</t>
+          <t>227739</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>207173</t>
+          <t>227739</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>207173</t>
+          <t>227739</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>51933</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>43276</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82658</t>
+          <t>70065</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>35281</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>30610</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>49095</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>87214</t>
+          <t>94879</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45666</t>
+          <t>79876</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113496</t>
+          <t>110878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>727230</t>
+          <t>517627</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>696505</t>
+          <t>503935</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>757430</t>
+          <t>530724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>444142</t>
+          <t>491496</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>435406</t>
+          <t>480907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>451964</t>
+          <t>499392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1171373</t>
+          <t>1009123</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1145091</t>
+          <t>993124</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1212921</t>
+          <t>1024126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>779163</t>
+          <t>574000</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>779163</t>
+          <t>574000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>779163</t>
+          <t>574000</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1258587</t>
+          <t>1104002</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1258587</t>
+          <t>1104002</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1258587</t>
+          <t>1104002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
